--- a/plantillas/25.xlsx
+++ b/plantillas/25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\isacs\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isac\Documents\Formulario Servicio\formulario-servicio\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8F070C-0A30-41AE-BB3A-AA6E8FCB1FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25633023-C529-48E6-9E73-FB927BC7882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -435,19 +435,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
@@ -457,35 +451,47 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -493,56 +499,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,242 +930,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="7"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:5" ht="47.1" customHeight="1">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" ht="24" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" ht="33.950000000000003" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="9" t="s">
+      <c r="D13" s="14"/>
+      <c r="E13" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="12.75" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="2"/>
+    <row r="14" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="2"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="33.950000000000003" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="10"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="24" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" ht="12.75" customHeight="1">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" ht="12.75" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="2"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="27" customHeight="1">
+      <c r="A18" s="23"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="36" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="2"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="10"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:5" ht="15.95" customHeight="1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="57.95" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="24"/>
     </row>
     <row r="26" spans="1:5" ht="69.2" customHeight="1">
-      <c r="A26" s="14"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
@@ -1198,23 +1189,9 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>